--- a/SMART RSA-RCS Training Datasets.xlsx
+++ b/SMART RSA-RCS Training Datasets.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DCAL HYD 2026\Paper\Theme\Responsive Services or RCS\Conceptualization\FESA RSA RCS PACKAGE PROJECTS\SMART RSA RCS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{91070554-1488-4950-A850-64FDB7F8F59C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6DDC87D2-7BF6-4E0C-AA0F-EB7119000E16}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="1" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Bulletin Board" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="588" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="102">
   <si>
     <t>RSA No</t>
   </si>
@@ -148,9 +148,6 @@
   </si>
   <si>
     <t>LINKED</t>
-  </si>
-  <si>
-    <t>RSA Risk / Hazard Category</t>
   </si>
   <si>
     <t>RSA Reliable/ Linked/ SMART/ Befitting Emergency</t>
@@ -342,6 +339,27 @@
   </si>
   <si>
     <t>DS Centre  Notice Alert</t>
+  </si>
+  <si>
+    <t>Explanation of terms:</t>
+  </si>
+  <si>
+    <t>CTA: Call To Attention issues</t>
+  </si>
+  <si>
+    <t>QOS: Quality of Service</t>
+  </si>
+  <si>
+    <t>QOPD: Quality of Performance Dimensions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ROC: RADIUS OF COVERAGE </t>
+  </si>
+  <si>
+    <t>FFC: Future Forward Contracts</t>
+  </si>
+  <si>
+    <t>RSA Risk / Hazard  Category</t>
   </si>
 </sst>
 </file>
@@ -709,20 +727,20 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:R6"/>
+  <dimension ref="A1:R14"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="8" max="8" width="15.109375" customWidth="1"/>
+    <col min="9" max="9" width="16.5546875" customWidth="1"/>
+    <col min="10" max="10" width="14.77734375" customWidth="1"/>
     <col min="13" max="13" width="15.21875" customWidth="1"/>
     <col min="14" max="14" width="14.77734375" customWidth="1"/>
-    <col min="15" max="15" width="25.21875" customWidth="1"/>
-    <col min="16" max="16" width="16.21875" customWidth="1"/>
-    <col min="17" max="17" width="28.33203125" customWidth="1"/>
+    <col min="15" max="15" width="14.21875" customWidth="1"/>
+    <col min="16" max="16" width="14.33203125" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -755,28 +773,28 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="K1" s="2" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="L1" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="1" t="s">
         <v>47</v>
       </c>
-      <c r="M1" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>48</v>
-      </c>
       <c r="P1" s="2" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Q1" s="2" t="s">
-        <v>39</v>
+        <v>101</v>
       </c>
       <c r="R1" s="1" t="s">
         <v>6</v>
@@ -808,10 +826,10 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
@@ -826,7 +844,7 @@
         <v>13</v>
       </c>
       <c r="P2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
         <v>36</v>
@@ -861,10 +879,10 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>13</v>
@@ -879,7 +897,7 @@
         <v>13</v>
       </c>
       <c r="P3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
         <v>36</v>
@@ -914,10 +932,10 @@
         <v>22</v>
       </c>
       <c r="J4" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
@@ -932,7 +950,7 @@
         <v>13</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -967,10 +985,10 @@
         <v>28</v>
       </c>
       <c r="J5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -985,7 +1003,7 @@
         <v>13</v>
       </c>
       <c r="P5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
         <v>36</v>
@@ -1020,10 +1038,10 @@
         <v>31</v>
       </c>
       <c r="J6" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
         <v>13</v>
@@ -1038,13 +1056,43 @@
         <v>13</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
         <v>36</v>
       </c>
       <c r="R6" t="s">
         <v>13</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D10" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D11" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D12" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D13" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="D14" t="s">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -1060,15 +1108,17 @@
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="8" max="8" width="13.77734375" customWidth="1"/>
+    <col min="9" max="9" width="18.5546875" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="14" width="14.77734375" customWidth="1"/>
-    <col min="15" max="17" width="32.44140625" customWidth="1"/>
-    <col min="18" max="18" width="23" customWidth="1"/>
+    <col min="11" max="11" width="9.77734375" customWidth="1"/>
+    <col min="12" max="12" width="10.33203125" customWidth="1"/>
+    <col min="13" max="13" width="10.6640625" customWidth="1"/>
+    <col min="14" max="14" width="10.109375" customWidth="1"/>
+    <col min="15" max="15" width="8.88671875" customWidth="1"/>
+    <col min="16" max="16" width="17.88671875" customWidth="1"/>
+    <col min="17" max="17" width="23.77734375" customWidth="1"/>
+    <col min="18" max="18" width="14.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="87" thickBot="1" x14ac:dyDescent="0.35">
@@ -1100,31 +1150,31 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="M1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="Q1" s="2" t="s">
-        <v>60</v>
-      </c>
       <c r="R1" s="1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="S1" s="1"/>
     </row>
@@ -1154,10 +1204,10 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
@@ -1172,7 +1222,7 @@
         <v>13</v>
       </c>
       <c r="P2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
         <v>36</v>
@@ -1207,10 +1257,10 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>13</v>
@@ -1225,7 +1275,7 @@
         <v>13</v>
       </c>
       <c r="P3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
         <v>36</v>
@@ -1263,7 +1313,7 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
@@ -1278,7 +1328,7 @@
         <v>13</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -1316,7 +1366,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -1331,7 +1381,7 @@
         <v>13</v>
       </c>
       <c r="P5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
         <v>36</v>
@@ -1369,7 +1419,7 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
         <v>13</v>
@@ -1384,7 +1434,7 @@
         <v>13</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
         <v>36</v>
@@ -1406,16 +1456,16 @@
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.109375" customWidth="1"/>
+    <col min="8" max="8" width="14.5546875" customWidth="1"/>
+    <col min="9" max="9" width="16.6640625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="14" width="14.77734375" customWidth="1"/>
-    <col min="15" max="15" width="29.44140625" customWidth="1"/>
+    <col min="12" max="13" width="12.77734375" customWidth="1"/>
+    <col min="14" max="14" width="13.88671875" customWidth="1"/>
+    <col min="15" max="15" width="15.6640625" customWidth="1"/>
+    <col min="16" max="16" width="10.44140625" customWidth="1"/>
     <col min="17" max="17" width="14.6640625" customWidth="1"/>
-    <col min="18" max="18" width="23" customWidth="1"/>
+    <col min="18" max="18" width="15.6640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -1447,31 +1497,31 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>67</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>68</v>
       </c>
       <c r="S1" s="1"/>
     </row>
@@ -1501,10 +1551,10 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
@@ -1519,7 +1569,7 @@
         <v>13</v>
       </c>
       <c r="P2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
         <v>36</v>
@@ -1554,10 +1604,10 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>13</v>
@@ -1572,7 +1622,7 @@
         <v>13</v>
       </c>
       <c r="P3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
         <v>36</v>
@@ -1610,7 +1660,7 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
@@ -1625,7 +1675,7 @@
         <v>13</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -1663,7 +1713,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -1678,7 +1728,7 @@
         <v>13</v>
       </c>
       <c r="P5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
         <v>36</v>
@@ -1716,7 +1766,7 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
         <v>13</v>
@@ -1731,7 +1781,7 @@
         <v>13</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
         <v>36</v>
@@ -1754,15 +1804,15 @@
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17.6640625" customWidth="1"/>
     <col min="10" max="10" width="16" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
     <col min="12" max="12" width="12.77734375" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="14" width="21.77734375" customWidth="1"/>
-    <col min="15" max="15" width="23.77734375" customWidth="1"/>
-    <col min="16" max="16" width="21.88671875" customWidth="1"/>
-    <col min="17" max="17" width="19.21875" customWidth="1"/>
+    <col min="13" max="13" width="7.77734375" customWidth="1"/>
+    <col min="14" max="14" width="10.21875" customWidth="1"/>
+    <col min="15" max="15" width="8.77734375" customWidth="1"/>
+    <col min="16" max="16" width="18.33203125" customWidth="1"/>
+    <col min="17" max="17" width="18" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1795,31 +1845,31 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="P1" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="O1" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>83</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>84</v>
       </c>
       <c r="S1" s="1"/>
     </row>
@@ -1849,10 +1899,10 @@
         <v>14</v>
       </c>
       <c r="J2" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
@@ -1920,10 +1970,10 @@
         <v>15</v>
       </c>
       <c r="P3" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q3" t="s">
         <v>86</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>87</v>
       </c>
       <c r="R3" t="s">
         <v>13</v>
@@ -1958,7 +2008,7 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
@@ -1973,7 +2023,7 @@
         <v>13</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -2011,7 +2061,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -2026,7 +2076,7 @@
         <v>13</v>
       </c>
       <c r="P5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
         <v>36</v>
@@ -2064,7 +2114,7 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
         <v>13</v>
@@ -2079,7 +2129,7 @@
         <v>13</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
         <v>36</v>
@@ -2101,16 +2151,16 @@
     <col min="1" max="1" width="13.6640625" customWidth="1"/>
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
-    <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
+    <col min="8" max="8" width="13.44140625" customWidth="1"/>
+    <col min="9" max="9" width="17.21875" customWidth="1"/>
+    <col min="10" max="10" width="15.33203125" customWidth="1"/>
     <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" customWidth="1"/>
+    <col min="12" max="12" width="9.6640625" customWidth="1"/>
+    <col min="13" max="13" width="10.5546875" customWidth="1"/>
     <col min="14" max="14" width="14.77734375" customWidth="1"/>
-    <col min="15" max="15" width="31.21875" customWidth="1"/>
-    <col min="16" max="16" width="30.21875" customWidth="1"/>
-    <col min="17" max="17" width="19.21875" customWidth="1"/>
+    <col min="15" max="15" width="10.5546875" customWidth="1"/>
+    <col min="16" max="16" width="18.88671875" customWidth="1"/>
+    <col min="17" max="17" width="16" customWidth="1"/>
     <col min="18" max="18" width="23" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2143,31 +2193,31 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>94</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>95</v>
       </c>
       <c r="S1" s="1"/>
     </row>
@@ -2215,10 +2265,10 @@
         <v>15</v>
       </c>
       <c r="P2" t="s">
+        <v>85</v>
+      </c>
+      <c r="Q2" t="s">
         <v>86</v>
-      </c>
-      <c r="Q2" t="s">
-        <v>87</v>
       </c>
       <c r="R2" t="s">
         <v>13</v>
@@ -2250,10 +2300,10 @@
         <v>20</v>
       </c>
       <c r="J3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>13</v>
@@ -2306,7 +2356,7 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
@@ -2321,7 +2371,7 @@
         <v>13</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -2359,7 +2409,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -2374,7 +2424,7 @@
         <v>13</v>
       </c>
       <c r="P5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
         <v>36</v>
@@ -2412,7 +2462,7 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
         <v>13</v>
@@ -2427,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
         <v>36</v>
@@ -2450,14 +2500,15 @@
     <col min="3" max="3" width="11.88671875" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
     <col min="8" max="8" width="16" customWidth="1"/>
-    <col min="9" max="9" width="26.44140625" customWidth="1"/>
-    <col min="10" max="10" width="16" customWidth="1"/>
-    <col min="11" max="11" width="12.33203125" customWidth="1"/>
-    <col min="12" max="12" width="12.77734375" customWidth="1"/>
-    <col min="13" max="13" width="15.21875" customWidth="1"/>
-    <col min="14" max="15" width="14.77734375" customWidth="1"/>
+    <col min="9" max="9" width="18.33203125" customWidth="1"/>
+    <col min="10" max="10" width="13.33203125" customWidth="1"/>
+    <col min="11" max="11" width="10" customWidth="1"/>
+    <col min="12" max="12" width="9.5546875" customWidth="1"/>
+    <col min="13" max="13" width="10.88671875" customWidth="1"/>
+    <col min="14" max="14" width="11.88671875" customWidth="1"/>
+    <col min="15" max="15" width="14.77734375" customWidth="1"/>
     <col min="17" max="17" width="19.21875" customWidth="1"/>
-    <col min="18" max="18" width="23" customWidth="1"/>
+    <col min="18" max="18" width="20.77734375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="115.8" thickBot="1" x14ac:dyDescent="0.35">
@@ -2489,31 +2540,31 @@
         <v>4</v>
       </c>
       <c r="J1" s="2" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="K1" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="L1" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="N1" s="1" t="s">
+      <c r="O1" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="O1" s="1" t="s">
+      <c r="P1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>76</v>
-      </c>
-      <c r="R1" s="1" t="s">
-        <v>77</v>
       </c>
       <c r="S1" s="1"/>
     </row>
@@ -2546,7 +2597,7 @@
         <v>16</v>
       </c>
       <c r="K2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L2" t="s">
         <v>13</v>
@@ -2561,7 +2612,7 @@
         <v>13</v>
       </c>
       <c r="P2" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q2" t="s">
         <v>36</v>
@@ -2599,7 +2650,7 @@
         <v>16</v>
       </c>
       <c r="K3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L3" t="s">
         <v>13</v>
@@ -2614,7 +2665,7 @@
         <v>13</v>
       </c>
       <c r="P3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q3" t="s">
         <v>36</v>
@@ -2652,7 +2703,7 @@
         <v>16</v>
       </c>
       <c r="K4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L4" t="s">
         <v>13</v>
@@ -2667,7 +2718,7 @@
         <v>13</v>
       </c>
       <c r="P4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q4" t="s">
         <v>36</v>
@@ -2705,7 +2756,7 @@
         <v>16</v>
       </c>
       <c r="K5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L5" t="s">
         <v>13</v>
@@ -2720,7 +2771,7 @@
         <v>13</v>
       </c>
       <c r="P5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q5" t="s">
         <v>36</v>
@@ -2758,7 +2809,7 @@
         <v>16</v>
       </c>
       <c r="K6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="L6" t="s">
         <v>13</v>
@@ -2773,7 +2824,7 @@
         <v>13</v>
       </c>
       <c r="P6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="Q6" t="s">
         <v>36</v>
